--- a/SapAriba_Google_Dispatcher/lib/net45/Data/Config.xlsx
+++ b/SapAriba_Google_Dispatcher/lib/net45/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{D843D15A-7D93-4D8C-8652-446054BD16A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3403F8EE-DF87-40E4-BED1-13D45DD4620E}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{D843D15A-7D93-4D8C-8652-446054BD16A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73BC8A44-2D8C-40FA-9CC8-D757692913E8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20700" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="103">
   <si>
     <t>Name</t>
   </si>
@@ -217,6 +217,12 @@
   </si>
   <si>
     <t xml:space="preserve">SAP Google Dispatcher Bot Status Report </t>
+  </si>
+  <si>
+    <t>MailMoveFolder</t>
+  </si>
+  <si>
+    <t>Google_Process_Mail</t>
   </si>
   <si>
     <t>BusinessExceptionLogs</t>
@@ -400,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -411,6 +417,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1030,30 +1037,38 @@
         <v>58</v>
       </c>
     </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
     <row r="43" spans="1:9" s="5" customFormat="1">
       <c r="A43" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="5" customFormat="1">
       <c r="A47" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1110,134 +1125,134 @@
     </row>
     <row r="2" spans="1:26" ht="30">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="30">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1263,13 +1278,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -1296,10 +1311,10 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
@@ -2307,14 +2322,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c4012d6b-a91c-4ec0-90d0-0537ad76586d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ef49ae6b-e58c-46b9-9be1-3da75242d3af" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2547,16 +2560,18 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c4012d6b-a91c-4ec0-90d0-0537ad76586d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ef49ae6b-e58c-46b9-9be1-3da75242d3af" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6BAF24C-4C87-4CB4-A3C1-51E93D7FACF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDE8327-4F64-4FFD-AAD2-6E125ABC8065}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2564,5 +2579,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDE8327-4F64-4FFD-AAD2-6E125ABC8065}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6BAF24C-4C87-4CB4-A3C1-51E93D7FACF9}"/>
 </file>
--- a/SapAriba_Google_Dispatcher/lib/net45/Data/Config.xlsx
+++ b/SapAriba_Google_Dispatcher/lib/net45/Data/Config.xlsx
@@ -2331,10 +2331,10 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010039B5D92226A63A4AA91620FECE37D35A" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9ba9c9a9cf21b1e77e33376b6b494bbf">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c4012d6b-a91c-4ec0-90d0-0537ad76586d" xmlns:ns3="ef49ae6b-e58c-46b9-9be1-3da75242d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ad5fe9437b422054d884ce493e37ba8" ns2:_="" ns3:_="">
-    <xsd:import namespace="c4012d6b-a91c-4ec0-90d0-0537ad76586d"/>
-    <xsd:import namespace="ef49ae6b-e58c-46b9-9be1-3da75242d3af"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010045A9A53AB2AD7C409EFC96CC55961B83" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9ff56ad652d5e5faec097a6229aaa81f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="649a79cd-06e4-47a3-aac9-21cb806f3675" xmlns:ns3="7f25b792-b2ba-4b5c-8669-b39a27555406" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3487cd39016dc6f53b8dc1d1dd8e1aa7" ns2:_="" ns3:_="">
+    <xsd:import namespace="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
+    <xsd:import namespace="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2343,15 +2343,16 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:Time" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
               </xsd:all>
@@ -2361,7 +2362,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c4012d6b-a91c-4ec0-90d0-0537ad76586d" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="649a79cd-06e4-47a3-aac9-21cb806f3675" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -2374,24 +2375,24 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -2408,21 +2409,26 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="Time" ma:index="20" nillable="true" ma:displayName="Time" ma:format="DateTime" ma:internalName="Time">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="21" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="22" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ef49ae6b-e58c-46b9-9be1-3da75242d3af" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7f25b792-b2ba-4b5c-8669-b39a27555406" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -2441,14 +2447,14 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{e4d20fd8-e210-4c2f-9702-d42025cd0699}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ef49ae6b-e58c-46b9-9be1-3da75242d3af">
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{2e954b58-32a8-4cab-baf9-92d5046718f0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="7f25b792-b2ba-4b5c-8669-b39a27555406">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -2562,10 +2568,11 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c4012d6b-a91c-4ec0-90d0-0537ad76586d">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ef49ae6b-e58c-46b9-9be1-3da75242d3af" xsi:nil="true"/>
+    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
+    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
@@ -2575,7 +2582,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBED6228-A11A-4906-B647-AAED7FE62F10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B320BD14-DC9D-4627-B780-5950CCE33889}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/SapAriba_Google_Dispatcher/lib/net45/Data/Config.xlsx
+++ b/SapAriba_Google_Dispatcher/lib/net45/Data/Config.xlsx
@@ -2331,10 +2331,10 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010045A9A53AB2AD7C409EFC96CC55961B83" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9ff56ad652d5e5faec097a6229aaa81f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="649a79cd-06e4-47a3-aac9-21cb806f3675" xmlns:ns3="7f25b792-b2ba-4b5c-8669-b39a27555406" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3487cd39016dc6f53b8dc1d1dd8e1aa7" ns2:_="" ns3:_="">
-    <xsd:import namespace="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
-    <xsd:import namespace="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010039B5D92226A63A4AA91620FECE37D35A" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9ba9c9a9cf21b1e77e33376b6b494bbf">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c4012d6b-a91c-4ec0-90d0-0537ad76586d" xmlns:ns3="ef49ae6b-e58c-46b9-9be1-3da75242d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3ad5fe9437b422054d884ce493e37ba8" ns2:_="" ns3:_="">
+    <xsd:import namespace="c4012d6b-a91c-4ec0-90d0-0537ad76586d"/>
+    <xsd:import namespace="ef49ae6b-e58c-46b9-9be1-3da75242d3af"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -2343,16 +2343,15 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:Time" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
               </xsd:all>
@@ -2362,7 +2361,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="649a79cd-06e4-47a3-aac9-21cb806f3675" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c4012d6b-a91c-4ec0-90d0-0537ad76586d" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -2375,24 +2374,24 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
@@ -2409,26 +2408,21 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="Time" ma:index="20" nillable="true" ma:displayName="Time" ma:format="DateTime" ma:internalName="Time">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="22" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="21" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7f25b792-b2ba-4b5c-8669-b39a27555406" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ef49ae6b-e58c-46b9-9be1-3da75242d3af" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -2447,14 +2441,14 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{2e954b58-32a8-4cab-baf9-92d5046718f0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="7f25b792-b2ba-4b5c-8669-b39a27555406">
+    <xsd:element name="TaxCatchAll" ma:index="18" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{e4d20fd8-e210-4c2f-9702-d42025cd0699}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ef49ae6b-e58c-46b9-9be1-3da75242d3af">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -2568,11 +2562,10 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c4012d6b-a91c-4ec0-90d0-0537ad76586d">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
-    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
+    <TaxCatchAll xmlns="ef49ae6b-e58c-46b9-9be1-3da75242d3af" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
@@ -2582,7 +2575,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B320BD14-DC9D-4627-B780-5950CCE33889}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBED6228-A11A-4906-B647-AAED7FE62F10}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
